--- a/네트워크 구성도.xlsx
+++ b/네트워크 구성도.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\작업방\기타\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git-remote-origin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF15DADB-9406-48C9-9ECF-0DFE59300654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FBFBCF-CC16-4DEA-99C5-2058A3F33C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4767E46D-E75F-4E0D-94DC-C06E60A75805}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4767E46D-E75F-4E0D-94DC-C06E60A75805}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,18 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>김기권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,6 +63,24 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -80,8 +107,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -767,9 +800,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93357E20-8FE2-49C6-9B9B-54A1446F30EA}">
-  <dimension ref="A1"/>
+  <dimension ref="C194:C195"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="194" spans="3:3" ht="38.25" x14ac:dyDescent="0.3">
+      <c r="C194" s="1"/>
+    </row>
+    <row r="195" spans="3:3" ht="31.5" x14ac:dyDescent="0.3">
+      <c r="C195" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
